--- a/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_WMT_Scenario.xlsx
+++ b/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_WMT_Scenario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0E6EB2-670F-4D01-975C-79B34B29BC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA9D9B-8560-47E0-BC20-4795E217091C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2275,10 +2275,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2470,7 +2466,9 @@
   <we:alternateReferences>
     <we:reference id="wa200009404" version="1.0.0.8" store="" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;af0763c3-055c-4d2a-adb1-950526411a32&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
